--- a/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Methylation Dictionary/GDC_Methylation_DM.xlsx
+++ b/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Methylation Dictionary/GDC_Methylation_DM.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjohnson/Projects/SDD-Dataset/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Methylation Dictionary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21924FEB-14FF-1F4C-A0C7-AB83FE162A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D7506A-D91E-0B46-8482-ED5AC1BE9E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12380" yWindow="8000" windowWidth="27240" windowHeight="16440"/>
+    <workbookView xWindow="-21660" yWindow="-1660" windowWidth="21600" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GDC_Methylation_DM" sheetId="1" r:id="rId1"/>
+    <sheet name="InfoSheet" sheetId="2" r:id="rId1"/>
+    <sheet name="Prefixes" sheetId="3" r:id="rId2"/>
+    <sheet name="Mapping Process" sheetId="4" r:id="rId3"/>
+    <sheet name="Timeline" sheetId="5" r:id="rId4"/>
+    <sheet name="New Concepts" sheetId="6" r:id="rId5"/>
+    <sheet name="Dictionary Mapping" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
   <si>
     <t>Column</t>
   </si>
@@ -76,9 +81,6 @@
     <t>Composite Element REF</t>
   </si>
   <si>
-    <t>sio:Identifier</t>
-  </si>
-  <si>
     <t>??composite_element</t>
   </si>
   <si>
@@ -100,9 +102,6 @@
     <t>Start</t>
   </si>
   <si>
-    <t>sio:Coordinate</t>
-  </si>
-  <si>
     <t>??chromosome_start_position</t>
   </si>
   <si>
@@ -115,24 +114,12 @@
     <t>Gene_Symbol</t>
   </si>
   <si>
-    <t>sio:Symbol</t>
-  </si>
-  <si>
     <t>??gene_symbol</t>
   </si>
   <si>
     <t>Gene Symbol</t>
   </si>
   <si>
-    <t>Gene_Type</t>
-  </si>
-  <si>
-    <t>ogg:0000000003</t>
-  </si>
-  <si>
-    <t>Gene Type</t>
-  </si>
-  <si>
     <t>Transcript_ID</t>
   </si>
   <si>
@@ -163,9 +150,6 @@
     <t>Feature_Type</t>
   </si>
   <si>
-    <t>mi:0116, ncit:C73619</t>
-  </si>
-  <si>
     <t>Feature Type</t>
   </si>
   <si>
@@ -178,9 +162,6 @@
     <t>ncit:C25431</t>
   </si>
   <si>
-    <t>go:ChromosomePositioning</t>
-  </si>
-  <si>
     <t>Chromosome start position</t>
   </si>
   <si>
@@ -193,14 +174,56 @@
     <t>ncit:C43568</t>
   </si>
   <si>
-    <t>sio:isPartOf</t>
+    <t>sio:SIO_000115</t>
+  </si>
+  <si>
+    <t>sio:SIO_000071</t>
+  </si>
+  <si>
+    <t>sio:SIO_000068</t>
+  </si>
+  <si>
+    <t>sio:SIO_000105</t>
+  </si>
+  <si>
+    <t>ncit:C73619</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>sio</t>
+  </si>
+  <si>
+    <t>http://semanticscience.org/resource/</t>
+  </si>
+  <si>
+    <t>ncit</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#</t>
+  </si>
+  <si>
+    <t>go</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/GO_</t>
+  </si>
+  <si>
+    <t>uo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/UO_</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -335,6 +358,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -517,7 +554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -632,8 +669,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -676,11 +728,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -714,6 +770,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1033,9 +1090,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A45D683-35B9-C54D-819E-053C6FFBDC89}">
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D26F671-685E-094B-A4AA-434A20443AEE}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{E735A1F7-8DE3-BF46-91A4-63EFFF8E80AC}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{B127609F-A4E1-BF4C-9DF4-D4626246B5AC}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{2F0BC291-EF11-3F45-9C46-A2BAB67369E8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5871302-D490-7E4E-9AE1-F5ACD69543BC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{570F66F2-CE0B-9A4B-A1B1-F1489A8AA995}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83B9772-1BA2-3346-BED4-0B64AD26FA6B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1095,10 +1248,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
       </c>
       <c r="N2" t="s">
         <v>17</v>
@@ -1106,162 +1259,159 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
         <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s">
         <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" t="s">
         <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
       </c>
       <c r="N12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -1269,13 +1419,10 @@
         <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N14" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
@@ -1283,30 +1430,16 @@
         <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="I15" t="s">
+        <v>51</v>
       </c>
       <c r="J15" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" t="s">
-        <v>57</v>
-      </c>
-      <c r="J16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
